--- a/output/pdf_financials_xlsx/HBFG.xlsx
+++ b/output/pdf_financials_xlsx/HBFG.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/HBFG.xlsx
+++ b/output/pdf_financials_xlsx/HBFG.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.106948</v>
+        <v>-0.106948</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.00567</v>
+        <v>0.00567</v>
       </c>
     </row>
     <row r="18">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2. BASIS OF PRESENTATION</t>
+          <t>2.    BASIS OF PRESENTATION</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Common Share Contributed Convertible Accumulated Controlling</t>
+          <t>Common      Share  Contributed    Convertible   Accumulated    Controlling</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Number of Share Contributed Convertible Accumulated Non-Controlling</t>
+          <t>Number of      Share  Contributed  Convertible  Accumulated  Non-Controlling</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">

--- a/output/pdf_financials_xlsx/HBFG.xlsx
+++ b/output/pdf_financials_xlsx/HBFG.xlsx
@@ -580,10 +580,10 @@
         <v>6.496645</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10.419658</v>
+        <v>9.444203999999999</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>27.758323</v>
       </c>
     </row>
     <row r="11">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009396</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.111027</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.193322</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.829333</v>
+        <v>-1.838729</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.158991</v>
+        <v>-2.270018</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.250628</v>
+        <v>-7.44395</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.388461</v>
+        <v>-1.397857</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.718446</v>
+        <v>-1.829473</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.287775</v>
+        <v>-6.481097</v>
       </c>
     </row>
     <row r="30">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-25.65710646972691</v>
+        <v>-25.83073336482122</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-21.46714461764859</v>
+        <v>-22.85411439468183</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-28.47035248671483</v>
+        <v>-29.34569320476481</v>
       </c>
     </row>
     <row r="31">
@@ -2536,10 +2536,10 @@
         <v>-0.154867</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>-0.071356</v>
+        <v>-0.441859</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.8470259999999999</v>
       </c>
     </row>
     <row r="125">
@@ -2552,10 +2552,10 @@
         <v>-0.154867</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-0.071356</v>
+        <v>-0.441859</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.8470259999999999</v>
       </c>
     </row>
     <row r="126">
@@ -4774,7 +4774,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6157,7 +6161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6252,7 +6256,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">

--- a/output/pdf_financials_xlsx/HBFG.xlsx
+++ b/output/pdf_financials_xlsx/HBFG.xlsx
@@ -751,11 +751,15 @@
       <c r="B20" s="3" t="n">
         <v>-1.829333</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>-2.265939</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>-7.244958</v>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -768,10 +772,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.078151</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>0.069063</v>
       </c>
     </row>
     <row r="22">
@@ -975,10 +979,8 @@
       <c r="C34" s="3" t="n">
         <v>3.486038</v>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" s="3" t="n">
+        <v>3.020627</v>
       </c>
     </row>
     <row r="35">
@@ -993,10 +995,8 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1011,10 +1011,8 @@
       <c r="C36" s="3" t="n">
         <v>3.486038</v>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D36" s="3" t="n">
+        <v>3.020627</v>
       </c>
     </row>
     <row r="37">
@@ -1024,15 +1022,13 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.263128</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.641157</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1047,10 +1043,8 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1065,10 +1059,8 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1083,10 +1075,8 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1101,10 +1091,8 @@
       <c r="C41" s="3" t="n">
         <v>0.720544</v>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D41" s="3" t="n">
+        <v>1.68336</v>
       </c>
     </row>
     <row r="42">
@@ -1119,10 +1107,8 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1137,10 +1123,8 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1155,10 +1139,8 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1173,10 +1155,8 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1191,10 +1171,8 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1209,10 +1187,8 @@
       <c r="C47" s="3" t="n">
         <v>0.302543</v>
       </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D47" s="3" t="n">
+        <v>0.327484</v>
       </c>
     </row>
     <row r="48">
@@ -1227,10 +1203,8 @@
       <c r="C48" s="3" t="n">
         <v>0.204172</v>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D48" s="3" t="n">
+        <v>0.257584</v>
       </c>
     </row>
     <row r="49">
@@ -1245,10 +1219,8 @@
       <c r="C49" s="3" t="n">
         <v>4.713297</v>
       </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D49" s="3" t="n">
+        <v>5.289055</v>
       </c>
     </row>
     <row r="50">
@@ -1263,10 +1235,8 @@
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1281,10 +1251,8 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1299,10 +1267,8 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1317,10 +1283,8 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1335,10 +1299,8 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1375,10 +1337,8 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1393,10 +1353,8 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1411,10 +1369,8 @@
       <c r="C58" s="3" t="n">
         <v>2.511601</v>
       </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D58" s="3" t="n">
+        <v>6.207796</v>
       </c>
     </row>
     <row r="59">
@@ -1429,10 +1385,8 @@
       <c r="C59" s="3" t="n">
         <v>0.413612</v>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D59" s="3" t="n">
+        <v>0.354142</v>
       </c>
     </row>
     <row r="60">
@@ -1447,10 +1401,8 @@
       <c r="C60" s="3" t="n">
         <v>1.059713</v>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D60" s="3" t="n">
+        <v>0.633007</v>
       </c>
     </row>
     <row r="61">
@@ -1465,10 +1417,8 @@
       <c r="C61" s="3" t="n">
         <v>0.643497</v>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D61" s="3" t="n">
+        <v>0.664614</v>
       </c>
     </row>
     <row r="62">
@@ -1483,10 +1433,8 @@
       <c r="C62" s="3" t="n">
         <v>4.628423</v>
       </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D62" s="3" t="n">
+        <v>7.859559</v>
       </c>
     </row>
     <row r="63">
@@ -1501,10 +1449,8 @@
       <c r="C63" s="3" t="n">
         <v>9.34172</v>
       </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D63" s="3" t="n">
+        <v>14.35683</v>
       </c>
     </row>
     <row r="64">
@@ -1514,15 +1460,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.457529</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.60117</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1537,10 +1481,8 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1555,10 +1497,8 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1568,15 +1508,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.227475</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.351134</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1591,10 +1529,8 @@
       <c r="C68" s="3" t="n">
         <v>1.05867</v>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D68" s="3" t="n">
+        <v>3.988212</v>
       </c>
     </row>
     <row r="69">
@@ -1609,10 +1545,8 @@
       <c r="C69" s="3" t="n">
         <v>0.027206</v>
       </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D69" s="3" t="n">
+        <v>0.07187499999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1627,10 +1561,8 @@
       <c r="C70" s="3" t="n">
         <v>0.195049</v>
       </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D70" s="3" t="n">
+        <v>0.544871</v>
       </c>
     </row>
     <row r="71">
@@ -1645,10 +1577,8 @@
       <c r="C71" s="3" t="n">
         <v>0.222255</v>
       </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D71" s="3" t="n">
+        <v>0.616746</v>
       </c>
     </row>
     <row r="72">
@@ -1663,10 +1593,8 @@
       <c r="C72" s="3" t="n">
         <v>0.388222</v>
       </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D72" s="3" t="n">
+        <v>1.029021</v>
       </c>
     </row>
     <row r="73">
@@ -1681,10 +1609,8 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1699,10 +1625,8 @@
       <c r="C74" s="3" t="n">
         <v>0.388222</v>
       </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D74" s="3" t="n">
+        <v>1.029021</v>
       </c>
     </row>
     <row r="75">
@@ -1717,10 +1641,8 @@
       <c r="C75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1735,10 +1657,8 @@
       <c r="C76" s="3" t="n">
         <v>1.435335</v>
       </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D76" s="3" t="n">
+        <v>4.789112</v>
       </c>
     </row>
     <row r="77">
@@ -1753,10 +1673,8 @@
       <c r="C77" s="3" t="n">
         <v>0.217628</v>
       </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1769,12 +1687,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.779562</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>4.355323</v>
       </c>
     </row>
     <row r="79">
@@ -1787,12 +1703,10 @@
         <v>0.244543</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0.217628</v>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.99719</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>4.355323</v>
       </c>
     </row>
     <row r="80">
@@ -1805,12 +1719,10 @@
         <v>-0.9338436060062032</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1809828584218294</v>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.9131553167775002</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1.887343623490042</v>
       </c>
     </row>
     <row r="81">
@@ -1825,10 +1737,8 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1843,10 +1753,8 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1861,10 +1769,8 @@
       <c r="C83" s="3" t="n">
         <v>0.105137</v>
       </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" s="3" t="n">
+        <v>0.048492</v>
       </c>
     </row>
     <row r="84">
@@ -1879,10 +1785,8 @@
       <c r="C84" s="3" t="n">
         <v>0.105137</v>
       </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D84" s="3" t="n">
+        <v>0.048492</v>
       </c>
     </row>
     <row r="85">
@@ -1895,12 +1799,10 @@
         <v>4.819921</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>5.153097</v>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.373535</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>2.406483</v>
       </c>
     </row>
     <row r="86">
@@ -1915,10 +1817,8 @@
       <c r="C86" s="3" t="n">
         <v>5.475862</v>
       </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D86" s="3" t="n">
+        <v>6.810298</v>
       </c>
     </row>
     <row r="87">
@@ -1933,10 +1833,8 @@
       <c r="C87" s="3" t="n">
         <v>6.911197</v>
       </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D87" s="3" t="n">
+        <v>11.722403</v>
       </c>
     </row>
     <row r="88">
@@ -1951,10 +1849,8 @@
       <c r="C88" s="3" t="n">
         <v>40.468178</v>
       </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D88" s="3" t="n">
+        <v>45.667234</v>
       </c>
     </row>
     <row r="89">
@@ -1969,10 +1865,8 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1987,10 +1881,8 @@
       <c r="C90" s="3" t="n">
         <v>-50.587238</v>
       </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D90" s="3" t="n">
+        <v>-58.278487</v>
       </c>
     </row>
     <row r="91">
@@ -2005,10 +1897,8 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2023,10 +1913,8 @@
       <c r="C92" s="3" t="n">
         <v>11.603526</v>
       </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D92" s="3" t="n">
+        <v>14.623702</v>
       </c>
     </row>
     <row r="93">
@@ -2041,10 +1929,8 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2059,10 +1945,8 @@
       <c r="C94" s="3" t="n">
         <v>2.176961</v>
       </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D94" s="3" t="n">
+        <v>2.399871</v>
       </c>
     </row>
     <row r="95">
@@ -2077,10 +1961,8 @@
       <c r="C95" s="3" t="n">
         <v>0.253562</v>
       </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D95" s="3" t="n">
+        <v>0.234556</v>
       </c>
     </row>
     <row r="96">
@@ -2095,10 +1977,8 @@
       <c r="C96" s="3" t="n">
         <v>2.430523</v>
       </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D96" s="3" t="n">
+        <v>2.634427</v>
       </c>
     </row>
     <row r="97">
@@ -2113,10 +1993,8 @@
       <c r="C97" s="3" t="n">
         <v>0.260179388806344</v>
       </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D97" s="3" t="n">
+        <v>0.1834964264395413</v>
       </c>
     </row>
     <row r="98">
@@ -2739,7 +2617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2791,23 +2669,27 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T: 416.626.6000  F: 416.626.8650 MNP.ca</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>As At Notes December 31, 2024 December</t>
+          <t>As At Notes December 31, 2025 December</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="5" t="n">
-        <v>0.002023</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F2" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -2837,10 +2719,8 @@
       <c r="F3" s="5" t="n">
         <v>3.486038</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>3.020627</v>
       </c>
     </row>
     <row r="4">
@@ -2856,7 +2736,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accounts and other receivable 6</t>
+          <t>Receivables 6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2864,16 +2744,16 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>0.263128</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F4" s="5" t="n">
         <v>0.720544</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G4" s="5" t="n">
+        <v>1.68336</v>
       </c>
     </row>
     <row r="5">
@@ -2889,7 +2769,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Equity investments 8</t>
+          <t>Equity investments</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2897,16 +2777,16 @@
           <t>EquityInvestments</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>0.309276</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.076899</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>0.025184</v>
       </c>
     </row>
     <row r="6">
@@ -2922,7 +2802,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inventory 9</t>
+          <t>Inventory 7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2930,16 +2810,16 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>0.215686</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.302543</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>0.327484</v>
       </c>
     </row>
     <row r="7">
@@ -2969,10 +2849,8 @@
       <c r="F7" s="5" t="n">
         <v>0.127273</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>0.2324</v>
       </c>
     </row>
     <row r="8">
@@ -2988,7 +2866,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Current assets total</t>
+          <t>Total Current Assets</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2996,16 +2874,16 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>2.144393</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F8" s="5" t="n">
         <v>4.713297</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>5.289055</v>
       </c>
     </row>
     <row r="9">
@@ -3021,26 +2899,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Loan receivable 7</t>
+          <t>Assets held for sale 22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LoansReceivable</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.2</v>
+          <t>AssetsHeldForSale</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="5" t="n">
+        <v>1.208216</v>
       </c>
     </row>
     <row r="10">
@@ -3051,7 +2929,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3068,10 +2946,8 @@
       <c r="F10" s="5" t="n">
         <v>0.194111</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" s="5" t="n">
+        <v>0.284546</v>
       </c>
     </row>
     <row r="11">
@@ -3082,12 +2958,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Property and equipment 10</t>
+          <t>Property and equipment 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3095,16 +2971,16 @@
           <t>NetPPE</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>2.32473</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
         <v>2.511601</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="5" t="n">
+        <v>6.207796</v>
       </c>
     </row>
     <row r="12">
@@ -3115,12 +2991,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Intangible assets 11</t>
+          <t>Intangible assets 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3128,16 +3004,16 @@
           <t>OtherIntangibleAssets</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>0.057679</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.413612</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G12" s="5" t="n">
+        <v>0.354142</v>
       </c>
     </row>
     <row r="13">
@@ -3148,12 +3024,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Investment in joint venture 12</t>
+          <t>Investment in joint venture 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -3165,10 +3041,8 @@
       <c r="F13" s="5" t="n">
         <v>0.270278</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G13" s="5" t="n">
+        <v>0.254513</v>
       </c>
     </row>
     <row r="14">
@@ -3179,25 +3053,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Interest in sublease 15</t>
+          <t>Interest in sublease 12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" s="5" t="n">
-        <v>0.221207</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F14" s="5" t="n">
         <v>0.179108</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G14" s="5" t="n">
+        <v>0.125555</v>
       </c>
     </row>
     <row r="15">
@@ -3208,12 +3082,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goodwill 13</t>
+          <t>Goodwill 11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3221,16 +3095,16 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>0.905239</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F15" s="5" t="n">
         <v>1.059713</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G15" s="5" t="n">
+        <v>0.633007</v>
       </c>
     </row>
     <row r="16">
@@ -3241,29 +3115,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOTAL ASSETS</t>
+          <t>Total non-current assets</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>5.853248</v>
+          <t>TotalNonCurrentAssets</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>9.34172</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.628423</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7.859559</v>
       </c>
     </row>
     <row r="17">
@@ -3274,29 +3148,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 14</t>
+          <t>TOTAL ASSETS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0.935398</v>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.05867</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.34172</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>14.35683</v>
       </c>
     </row>
     <row r="18">
@@ -3312,22 +3186,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contingent consideration 5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.08841</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.05867</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.988212</v>
       </c>
     </row>
     <row r="19">
@@ -3343,19 +3219,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Current portion of long-term debt 16</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CurrentDebt</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0.071647</v>
+          <t>Contingent consideration 5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.027206</v>
+        <v>0.08841</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3376,24 +3250,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Current portion of lease liabilities 15</t>
+          <t>Current portion of long-term debt 13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CurrentCapitalLeaseObligation</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.207093</v>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.195049</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027206</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.07187499999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3409,24 +3283,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Current portion of deferred revenue 17</t>
+          <t>Current portion of lease liabilities 12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CurrentDeferredRevenue</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0.135</v>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.195049</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.544871</v>
       </c>
     </row>
     <row r="22">
@@ -3442,24 +3316,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Current liabilities total</t>
+          <t>Current portion of deferred revenue 14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1.349138</v>
+          <t>CurrentDeferredRevenue</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1.435335</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.066</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.184154</v>
       </c>
     </row>
     <row r="23">
@@ -3475,24 +3349,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Long-term debt 16</t>
+          <t>Total current liabilities</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0.244543</v>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.217628</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.435335</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>4.789112</v>
       </c>
     </row>
     <row r="24">
@@ -3508,20 +3382,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Convertible debentures 16</t>
+          <t>Liabilities held for sale 22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>3.155455</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>2.985313</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.122993</v>
       </c>
     </row>
     <row r="25">
@@ -3532,20 +3408,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lease liabilities 15</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>1.664466</v>
+          <t>Long-term debt 13</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LongTermDebt</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.779562</v>
+        <v>0.217628</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3561,31 +3443,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deferred revenue 17</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CurrentDeferredRevenue</t>
-        </is>
-      </c>
+          <t>Convertible debentures 13</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.388222</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.985313</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.377462</v>
       </c>
     </row>
     <row r="27">
@@ -3596,17 +3472,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Deferred tax liability 24</t>
+          <t>Lease liabilities 12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NonCurrentDeferredTaxesLiabilities</t>
+          <t>LongTermCapitalLeaseObligation</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3615,12 +3491,10 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.105137</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.779562</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>4.355323</v>
       </c>
     </row>
     <row r="28">
@@ -3631,29 +3505,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES</t>
+          <t>Deferred revenue 14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>6.413602</v>
+          <t>CurrentDeferredRevenue</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>6.911197</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.388222</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1.029021</v>
       </c>
     </row>
     <row r="29">
@@ -3664,29 +3538,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Share capital 18</t>
+          <t>Deferred tax liability 21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>35.472973</v>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>40.468178</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.105137</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.048492</v>
       </c>
     </row>
     <row r="30">
@@ -3697,25 +3571,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Convertible debenture-equity portion 16</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0.690099</v>
+          <t>Total non-current liabilities</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.692495</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.475862</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6.810298</v>
       </c>
     </row>
     <row r="31">
@@ -3726,29 +3604,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Contributed surplus 18</t>
+          <t>TOTAL LIABILITIES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>11.344311</v>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>11.603526</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.911197</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>11.722403</v>
       </c>
     </row>
     <row r="32">
@@ -3764,24 +3642,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Share capital 15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>-48.230606</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-50.587238</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>40.468178</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>45.667234</v>
       </c>
     </row>
     <row r="33">
@@ -3797,24 +3675,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TOTAL SHAREHOLDERS’ EQUITY</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>-0.7232229999999999</v>
+          <t>Convertible debenture-equity portion 13</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>2.176961</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.692495</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.387422</v>
       </c>
     </row>
     <row r="34">
@@ -3830,24 +3704,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Contributed surplus 15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MinorityInterest</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0.162869</v>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.253562</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.603526</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>14.623702</v>
       </c>
     </row>
     <row r="35">
@@ -3863,24 +3737,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TOTAL EQUITY</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TotalEquityGrossMinorityInterest</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.560354</v>
+        <v>-48.230606</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>2.430523</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-50.587238</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-58.278487</v>
       </c>
     </row>
     <row r="36">
@@ -3896,313 +3768,323 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND EQUITY</t>
+          <t>TOTAL SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>5.853248</v>
+        <v>-0.7232229999999999</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>9.34172</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.176961</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2.399871</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Non-controlling interest</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>MinorityInterest</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-1.829333</v>
+        <v>0.162869</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-2.34409</v>
+        <v>0.253562</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-7.314021</v>
+        <v>0.234556</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Amortization 8,9</t>
+          <t>TOTAL EQUITY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-0.560354</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.440545</v>
+        <v>2.430523</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.962853</v>
+        <v>2.634427</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Financing costs 12,13</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TOTAL LIABILITIES AND EQUITY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>5.853248</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.5630810000000001</v>
+        <v>9.34172</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.634859</v>
+        <v>14.35683</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Items not affecting cash and cash equivalents</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Financing income on sublease 12</t>
+          <t>As At Notes December 31, 2024 December</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.021478</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>-0.018001</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Expected credit loss 6</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts and other receivable 6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.263128</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.239113</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.299195</v>
+        <v>0.720544</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Share-based compensation 15</t>
+          <t>Equity investments 8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EquityInvestments</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.309276</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.289815</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>3.69265</v>
+        <v>0.076899</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bonuses paid in shares</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Inventory 9</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.215686</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.1185</v>
+        <v>0.302543</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Loss on contingent consideration 5</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.5860570000000001</v>
+          <t>Current assets total</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>2.144393</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>4.713297</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Loss on recognition of sublease asset</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0.007818</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.019291</v>
+          <t>Loan receivable 7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Deferred tax recovery</t>
+          <t>Prepaids long-term</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4212,86 +4094,94 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.106948</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.00567</v>
+        <v>0.194111</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Share of income from investment in joint venture 10</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Property and equipment 10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>2.32473</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-0.020278</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.015765</v>
+        <v>2.511601</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.092159</v>
+          <t>Intangible assets 11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.057679</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.413612</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Changes in fair value of equity investment</t>
+          <t>Investment in joint venture 12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4301,179 +4191,201 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.19056</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.051715</v>
+        <v>0.270278</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents total</t>
+          <t>Interest in sublease 15</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>-0.87294</v>
+        <v>0.221207</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.7223619999999999</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-1.037626</v>
+        <v>0.179108</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital related to operations 19</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Goodwill 13</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.905239</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.221841</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>1.988101</v>
+        <v>1.059713</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) operating activities-continued operations</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>5.853248</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.944203</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.950475</v>
+        <v>9.34172</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities-discontinued operations</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities 14</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.935398</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.055665</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.032835</v>
+        <v>1.05867</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Property and equipment additions 8</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current portion of long-term debt 16</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.071647</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.141177</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-1.275591</v>
+        <v>0.027206</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Proceeds on sale of equity investments</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current portion of lease liabilities 15</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.207093</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.041817</v>
+        <v>0.195049</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4484,176 +4396,192 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cash acquired in acquisition 5</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current portion of deferred revenue 17</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentDeferredRevenue</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.135</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.254772</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.00516</v>
+        <v>0.066</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Proceeds from sublease 12</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current liabilities total</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>1.349138</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.051853</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.052263</v>
+        <v>1.435335</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Consideration issued in acquisitions 5</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Long-term debt 16</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LongTermDebt</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.244543</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.14065</v>
+        <v>0.217628</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Convertible debentures 16</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>-0.35068</v>
+        <v>3.155455</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-0.012735</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-1.358818</v>
+        <v>2.985313</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Proceeds from a share private placement 15</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.5</v>
+          <t>Lease liabilities 15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>1.664466</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>1.779562</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Proceeds from convertible debentures 13</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Deferred revenue 17</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CurrentDeferredRevenue</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>3</v>
+        <v>0.388222</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4664,22 +4592,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt 13</t>
+          <t>Deferred tax liability 24</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RepaymentOfDebt</t>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4688,69 +4616,73 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.071356</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.105137</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Proceeds from stock option exercises 15</t>
+          <t>TOTAL LIABILITIES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ProceedsFromStockOptionExercised</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>6.413602</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.288</v>
+        <v>6.911197</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Proceeds from warrant exercises 15</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital 18</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>35.472973</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.441</v>
+        <v>40.468178</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4761,63 +4693,63 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lease payments 12</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>RepaymentOfDebt</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Convertible debenture-equity portion 16</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>0.690099</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>-0.370503</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>-0.826226</v>
+        <v>0.692495</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities- continuing operations</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Contributed surplus 18</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>11.344311</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>3.149141</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.059026</v>
+        <v>11.603526</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4828,25 +4760,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cash flows used in financing activities – discontinued operations</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>-1.829333</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.030875</v>
+        <v>-2.34409</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.030877</v>
+        <v>-7.314021</v>
       </c>
     </row>
     <row r="68">
@@ -4857,17 +4791,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>(Decrease)/increase in cash and cash equivalents</t>
+          <t>Amortization 8,9</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4876,10 +4810,10 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>2.216993</v>
+        <v>0.440545</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.465411</v>
+        <v>0.962853</v>
       </c>
     </row>
     <row r="69">
@@ -4890,27 +4824,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>1.10196</v>
+          <t>Financing costs 12,13</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>1.269045</v>
+        <v>0.5630810000000001</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>3.486038</v>
+        <v>0.634859</v>
       </c>
     </row>
     <row r="70">
@@ -4921,27 +4853,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>1.269045</v>
+          <t>Financing income on sublease 12</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>3.486038</v>
+        <v>-0.021478</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>3.020627</v>
+        <v>-0.018001</v>
       </c>
     </row>
     <row r="71">
@@ -4952,12 +4882,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.    BASIS OF PRESENTATION</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Certain comparative amounts have been reclassified to conform with current accounting presentation. of Directors as of April</t>
+          <t>Expected credit loss 6</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -4967,10 +4897,10 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.002026</v>
+        <v>0.239113</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.299195</v>
       </c>
     </row>
     <row r="72">
@@ -4986,24 +4916,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Amortization 10,11</t>
+          <t>Share-based compensation 15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0.440872</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.479568</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.289815</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>3.69265</v>
       </c>
     </row>
     <row r="73">
@@ -5019,20 +4949,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Financing costs 15,16</t>
+          <t>Bonuses paid in shares</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>0.416042</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.570404</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0395</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.1185</v>
       </c>
     </row>
     <row r="74">
@@ -5048,7 +4978,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Financing income on sublease 15</t>
+          <t>Loss on contingent consideration 5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5057,13 +4987,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>-0.021478</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.5860570000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5079,7 +5009,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Expected credit loss 6,7</t>
+          <t>Loss on recognition of sublease asset</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5089,12 +5019,10 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.239113</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007818</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.019291</v>
       </c>
     </row>
     <row r="76">
@@ -5110,24 +5038,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Share-based compensation 18</t>
+          <t>Deferred tax recovery</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>0.055972</v>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.289815</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.106948</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.00567</v>
       </c>
     </row>
     <row r="77">
@@ -5143,7 +5071,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bonus paid in shares</t>
+          <t>Share of income from investment in joint venture 10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5153,12 +5081,10 @@
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.020278</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.015765</v>
       </c>
     </row>
     <row r="78">
@@ -5174,22 +5100,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gain on early renewal of lease 15</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>-0.008333</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" s="5" t="n">
+        <v>-0.092159</v>
       </c>
     </row>
     <row r="79">
@@ -5205,20 +5131,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Loss (gain) on recognition of sublease 15</t>
+          <t>Changes in fair value of equity investment</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>0.05184</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.007818</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19056</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.051715</v>
       </c>
     </row>
     <row r="80">
@@ -5234,22 +5160,18 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Deferred tax recovery 24</t>
+          <t>Items not affecting cash and cash equivalents total</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="5" t="n">
+        <v>-0.87294</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.106948</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.7223619999999999</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-1.037626</v>
       </c>
     </row>
     <row r="81">
@@ -5265,7 +5187,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Share of income from investment in joint venture 12</t>
+          <t>Net change in non-cash working capital related to operations 19</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5275,12 +5197,10 @@
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>-0.020278</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.221841</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1.988101</v>
       </c>
     </row>
     <row r="82">
@@ -5296,7 +5216,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Unrealized loss on equity investment 8</t>
+          <t>Cash flows from (used in) operating activities-continued operations</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -5306,12 +5226,10 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.19056</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.944203</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.950475</v>
       </c>
     </row>
     <row r="83">
@@ -5327,20 +5245,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital related to operations 22</t>
+          <t>Cash flows from operating activities-discontinued operations</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.150017</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-0.290673</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.055665</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.032835</v>
       </c>
     </row>
     <row r="84">
@@ -5351,29 +5269,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Items not affecting cash and cash equivalents</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>-0.722923</v>
+          <t>Property and equipment additions 8</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.888538</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.141177</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-1.275591</v>
       </c>
     </row>
     <row r="85">
@@ -5389,17 +5303,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Intangible asset dispositions (expenditures) 11</t>
+          <t>Proceeds on sale of equity investments</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>0.00252</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.041817</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5420,20 +5334,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Property and equipment expenditures 10</t>
+          <t>Cash acquired in acquisition 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>-0.3532</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.141177</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.254772</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.00516</v>
       </c>
     </row>
     <row r="87">
@@ -5449,7 +5363,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Proceeds on sale of equity investments 8</t>
+          <t>Proceeds from sublease 12</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -5459,12 +5373,10 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.041817</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.051853</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.052263</v>
       </c>
     </row>
     <row r="88">
@@ -5480,7 +5392,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Acquired cash 5</t>
+          <t>Consideration issued in acquisitions 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -5490,12 +5402,10 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.254772</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.22</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.14065</v>
       </c>
     </row>
     <row r="89">
@@ -5511,20 +5421,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Proceeds from sublease 15</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
-        <v>0.037955</v>
+        <v>-0.35068</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.051853</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.012735</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-1.358818</v>
       </c>
     </row>
     <row r="90">
@@ -5535,27 +5447,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Corporate acquisition 5</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Proceeds from a share private placement 15</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="91">
@@ -5571,12 +5487,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Proceeds from convertible debentures 16</t>
+          <t>Proceeds from convertible debentures 13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>1.645</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>3</v>
@@ -5600,7 +5518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt 16</t>
+          <t>Repayment of long-term debt 13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5608,16 +5526,16 @@
           <t>RepaymentOfDebt</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
-        <v>-0.154867</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" s="5" t="n">
         <v>-0.071356</v>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G92" s="5" t="n">
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="93">
@@ -5633,7 +5551,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Proceeds from stock option exercises 18</t>
+          <t>Proceeds from stock option exercises 15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5649,10 +5567,8 @@
       <c r="F93" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>0.288</v>
       </c>
     </row>
     <row r="94">
@@ -5668,12 +5584,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Proceeds from warrant exercises 18</t>
+          <t>Proceeds from warrant exercises 15</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>0.002</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" s="5" t="n">
         <v>0.441</v>
@@ -5697,20 +5615,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lease liabilities settled 15</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>-0.2894</v>
+          <t>Lease payments 12</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>-0.401378</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.370503</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.826226</v>
       </c>
     </row>
     <row r="96">
@@ -5726,24 +5648,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>1.240688</v>
+          <t>Cash flows from financing activities- continuing operations</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>3.118266</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.149141</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-0.059026</v>
       </c>
     </row>
     <row r="97">
@@ -5759,24 +5677,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>0.167085</v>
+          <t>Cash flows used in financing activities – discontinued operations</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>2.216993</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.030875</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-0.030877</v>
       </c>
     </row>
     <row r="98">
@@ -5787,25 +5701,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>1.269045</v>
+          <t>(Decrease)/increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.911232</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.216993</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.465411</v>
       </c>
     </row>
     <row r="99">
@@ -5816,72 +5734,74 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cash equivalents</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>1.10196</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>2.574806</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.269045</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>3.486038</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Product sales</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>1.269045</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>6.864145</v>
+        <v>3.486038</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>18.053167</v>
+        <v>3.020627</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>2.    BASIS OF PRESENTATION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Franchise revenue 14</t>
+          <t>Certain comparative amounts have been reclassified to conform with current accounting presentation. of Directors as of April</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -5891,277 +5811,279 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.947815</v>
+        <v>0.002026</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>2.822217</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Consulting and services</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization 10,11</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.440872</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.193045</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>1.209959</v>
+        <v>0.479568</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Total Revenues</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Financing costs 15,16</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>0.416042</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>8.005005000000001</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>22.085343</v>
+        <v>0.570404</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Direct operating costs</t>
+          <t>Financing income on sublease 15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
-        <v>2.448969</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>3.211011</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>10.005393</v>
+        <v>-0.021478</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>General and administrative 18</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Expected credit loss 6,7</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>2.623356</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>5.307354</v>
+        <v>0.239113</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salaries and wages 18</t>
+          <t>Share-based compensation 18</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.055972</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>2.640364</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>7.490878</v>
+        <v>0.289815</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 8,9</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Bonus paid in shares</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.440545</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>0.962853</v>
+        <v>0.0395</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Expected credit loss 6</t>
+          <t>Gain on early renewal of lease 15</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>0.239113</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>0.299195</v>
+      <c r="E108" s="5" t="n">
+        <v>-0.008333</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Share-based compensation 15</t>
+          <t>Loss (gain) on recognition of sublease 15</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="5" t="n">
+        <v>0.05184</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.289815</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>3.69265</v>
+        <v>0.007818</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Deferred tax recovery 24</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6170,59 +6092,59 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>9.444203999999999</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>27.758323</v>
+        <v>-0.106948</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Net loss from operations</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Share of income from investment in joint venture 12</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-1.439199</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>-5.67298</v>
+        <v>-0.020278</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Financing costs 12,13</t>
+          <t>Unrealized loss on equity investment 8</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -6232,146 +6154,150 @@
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>-0.944766</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>-1.155865</v>
+        <v>0.19056</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Net change in non-cash working capital related to operations 22</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="n">
-        <v>0.009396</v>
+        <v>0.150017</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.111027</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>0.193322</v>
+        <v>-0.290673</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Items not affecting cash and cash equivalents</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Income/(loss) from investment in joint venture 10</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-0.722923</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.020278</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>-0.015765</v>
+        <v>-0.888538</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Loss on recognition/derecognition of sublease</t>
+          <t>Intangible asset dispositions (expenditures) 11</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>-0.007818</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>-0.019291</v>
+      <c r="E115" s="5" t="n">
+        <v>0.00252</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Loss on contingent consideration 5</t>
+          <t>Property and equipment expenditures 10</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>-0.5860570000000001</v>
+      <c r="E116" s="5" t="n">
+        <v>-0.3532</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>-0.141177</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Changes in fair value of equity investment</t>
+          <t>Proceeds on sale of equity investments 8</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -6381,86 +6307,88 @@
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>-0.19056</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>-0.051715</v>
+        <v>0.041817</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss before taxes</t>
+          <t>Acquired cash 5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" s="5" t="n">
-        <v>-1.829333</v>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>-2.451038</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>-7.308351</v>
+        <v>0.254772</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Deferred income tax (expense)/recovery 21</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from sublease 15</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>0.037955</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.106948</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>-0.00567</v>
+        <v>0.051853</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss from continuing operations</t>
+          <t>Corporate acquisition 5</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -6470,216 +6398,228 @@
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>-2.34409</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>-7.314021</v>
+        <v>-0.22</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Net income from discontinued operations 22</t>
+          <t>Proceeds from convertible debentures 16</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="5" t="n">
+        <v>1.645</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.078151</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>0.069063</v>
+        <v>3</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Net loss attributable to the owners of the Company</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Repayment of long-term debt 16</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="n">
-        <v>-1.921996</v>
+        <v>-0.154867</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>-2.356632</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>-7.691249</v>
+        <v>-0.071356</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Net income attributable to non-controlling interest</t>
+          <t>Proceeds from stock option exercises 18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>-0.092663</v>
+          <t>ProceedsFromStockOptionExercised</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>-0.090693</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>-0.446291</v>
+        <v>0.15</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Proceeds from warrant exercises 18</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" s="5" t="n">
-        <v>-1.829333</v>
+        <v>0.002</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-2.265939</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>-7.244958</v>
+        <v>0.441</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Lease liabilities settled 15</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>-0.2894</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>120.94241</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>129.97064</v>
+        <v>-0.401378</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Common      Share  Contributed    Convertible   Accumulated    Controlling</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 110,503,835 35,472,973 11,344,311 690,099 (48,230,606)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>1.240688</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>-0.560354</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.162869</v>
+        <v>3.118266</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination and investment in joint venture 5,11 2,285,805 723,387 - - -</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0.167085</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0.723387</v>
+        <v>2.216993</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6690,27 +6630,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Warrants exercise 17 2,995,000 599,600 (600) - -</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="5" t="n">
+        <v>1.269045</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.599</v>
+        <v>0.911232</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6721,17 +6659,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Stock options exercise 17 410,000 180,000 (30,000) - -</t>
+          <t>Cash equivalents</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -6741,7 +6679,7 @@
         </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.15</v>
+        <v>2.574806</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6757,12 +6695,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Share based compensation 17 - - 289,815 - -</t>
+          <t>Product sales</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -6772,12 +6710,10 @@
         </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.289815</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.864145</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>18.053167</v>
       </c>
     </row>
     <row r="131">
@@ -6788,12 +6724,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Debt settlement 96,153 37,500 - - -</t>
+          <t>Franchise revenue 14</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -6803,12 +6739,10 @@
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.947815</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2.822217</v>
       </c>
     </row>
     <row r="132">
@@ -6819,12 +6753,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Convertible debentures issued 15 - - - 555,537 -</t>
+          <t>Consulting and services</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -6834,12 +6768,10 @@
         </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.5555369999999999</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.193045</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>1.209959</v>
       </c>
     </row>
     <row r="133">
@@ -6850,27 +6782,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Issued pursuant to business combination</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Conversion of convertible debentures 15 12,735,246 3,454,718 - (453,946) -</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Total Revenues</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>3.000772</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.005005000000001</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>22.085343</v>
       </c>
     </row>
     <row r="134">
@@ -6881,27 +6815,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax impact - - - (99,195) -</t>
+          <t>Direct operating costs</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="5" t="n">
+        <v>2.448969</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.09919500000000001</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.211011</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>10.005393</v>
       </c>
     </row>
     <row r="135">
@@ -6912,25 +6842,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - (2,356,632)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>General and administrative 18</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>-2.265939</v>
+        <v>2.623356</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.090693</v>
+        <v>5.307354</v>
       </c>
     </row>
     <row r="136">
@@ -6941,25 +6875,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Balance at December 31,2024 129,026,039 40,468,178 11,603,526 692,495 (50,587,238)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Salaries and wages 18</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
-        <v>2.430523</v>
+        <v>2.640364</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.253562</v>
+        <v>7.490878</v>
       </c>
     </row>
     <row r="137">
@@ -6970,27 +6908,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shares issued on Smile Tiger</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Shares issued on Smile Tiger business acquisition 5 104,854 125,000 - - -</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Depreciation and amortization 8,9</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.440545</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.962853</v>
       </c>
     </row>
     <row r="138">
@@ -7001,12 +6941,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Franchising Inc. business</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Franchising Inc. business acquisition 5 272,479 300,000 - - -</t>
+          <t>Expected credit loss 6</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -7016,10 +6956,10 @@
         </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.334382</v>
+        <v>0.239113</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.034382</v>
+        <v>0.299195</v>
       </c>
     </row>
     <row r="139">
@@ -7030,12 +6970,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Franchising Inc. business</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Shares issued on Via Cibo earn-out 5 399,093 674,467 - - -</t>
+          <t>Share-based compensation 15</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -7045,12 +6985,10 @@
         </is>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0.674467</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.289815</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>3.69265</v>
       </c>
     </row>
     <row r="140">
@@ -7061,27 +6999,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Issuance of common shares on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Issuance of common shares on private placement 17 333,333 409,431 90,569 - -</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.444203999999999</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>27.758323</v>
       </c>
     </row>
     <row r="141">
@@ -7092,27 +7032,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Issuance of common shares on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Share based compensation 17 - - 3,692,650 - -</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Net loss from operations</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
-        <v>3.69265</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.439199</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-5.67298</v>
       </c>
     </row>
     <row r="142">
@@ -7123,12 +7065,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Issuance of common shares on</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Stock options exercise 585,000 432,837 (144,837) - -</t>
+          <t>Financing costs 12,13</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -7138,12 +7080,10 @@
         </is>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.944766</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-1.155865</v>
       </c>
     </row>
     <row r="143">
@@ -7154,27 +7094,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Issuance of common shares on</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Non-controlling interest buyout 5 613,468 895,663 (395,984) - -</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.009396</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.111027</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>-0.499679</v>
+        <v>0.193322</v>
       </c>
     </row>
     <row r="144">
@@ -7185,12 +7125,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Issuance of common shares on</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Treasury shares sold 5 - 222,222 (222,222) - -</t>
+          <t>Income/(loss) from investment in joint venture 10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -7199,15 +7139,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F144" s="5" t="n">
+        <v>0.020278</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>-0.015765</v>
       </c>
     </row>
     <row r="145">
@@ -7218,12 +7154,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Issuance of common shares on</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Convertible debenture exercise 2,666,667 2,139,436 - (367,388) -</t>
+          <t>Loss on recognition/derecognition of sublease</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -7233,12 +7169,10 @@
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>1.772048</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007818</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-0.019291</v>
       </c>
     </row>
     <row r="146">
@@ -7249,12 +7183,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax impact - - - 62,315 -</t>
+          <t>Loss on contingent consideration 5</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -7263,13 +7197,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F146" s="5" t="n">
-        <v>0.062315</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>-0.5860570000000001</v>
       </c>
     </row>
     <row r="147">
@@ -7280,12 +7214,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - (7,691,249)</t>
+          <t>Changes in fair value of equity investment</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -7295,10 +7229,10 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-7.244958</v>
+        <v>-0.19056</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.446291</v>
+        <v>-0.051715</v>
       </c>
     </row>
     <row r="148">
@@ -7309,25 +7243,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Balance at December 31,2025 134,000,933 45,667,234 14,623,702 387,422 (58,278,487)</t>
+          <t>Loss and comprehensive loss before taxes</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E148" s="5" t="n">
+        <v>-1.829333</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>2.634427</v>
+        <v>-2.451038</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.234556</v>
+        <v>-7.308351</v>
       </c>
     </row>
     <row r="149">
@@ -7338,25 +7270,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Product sales 3,23</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" s="5" t="n">
-        <v>5.070922</v>
+          <t>Deferred income tax (expense)/recovery 21</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>7.92815</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.106948</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>-0.00567</v>
       </c>
     </row>
     <row r="150">
@@ -7367,25 +7303,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Franchise revenue 3,17</t>
+          <t>Net loss and comprehensive loss from continuing operations</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>0.19309</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.947815</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.34409</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>-7.314021</v>
       </c>
     </row>
     <row r="151">
@@ -7396,25 +7332,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Consulting and services 3</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>0.147592</v>
+          <t>Net income from discontinued operations 22</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.193045</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.078151</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.069063</v>
       </c>
     </row>
     <row r="152">
@@ -7425,29 +7365,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Net loss attributable to the owners of the Company</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" s="5" t="n">
-        <v>5.411604</v>
+        <v>-1.921996</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>9.06901</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.356632</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>-7.691249</v>
       </c>
     </row>
     <row r="153">
@@ -7458,29 +7392,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>General and administrative 21</t>
+          <t>Net income attributable to non-controlling interest</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2.097402</v>
+        <v>-0.092663</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>3.08047</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.090693</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>-0.446291</v>
       </c>
     </row>
     <row r="154">
@@ -7491,29 +7423,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Salaries and wages 21</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1.452481</v>
+        <v>-1.829333</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>2.717138</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.265939</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>-7.244958</v>
       </c>
     </row>
     <row r="155">
@@ -7524,29 +7454,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Depreciation and Amortization 10,11</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="n">
-        <v>0.440872</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>0.479568</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>120.94241</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>129.97064</v>
       </c>
     </row>
     <row r="156">
@@ -7557,25 +7487,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common      Share  Contributed    Convertible   Accumulated    Controlling</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Expected credit loss 6,7</t>
+          <t>Balance at December 31, 2023 110,503,835 35,472,973 11,344,311 690,099 (48,230,606)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" s="5" t="n">
-        <v>0.00095</v>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.239113</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.560354</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.162869</v>
       </c>
     </row>
     <row r="157">
@@ -7586,20 +7516,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Share-based compensation 18</t>
+          <t>Issued pursuant to business combination and investment in joint venture 5,11 2,285,805 723,387 - - -</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" s="5" t="n">
-        <v>0.055971</v>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.289815</v>
+        <v>0.723387</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7615,24 +7547,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>6.496645</v>
+          <t>Warrants exercise 17 2,995,000 599,600 (600) - -</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>10.419658</v>
+        <v>0.599</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7648,24 +7578,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="n">
-        <v>-1.085041</v>
+          <t>Stock options exercise 17 410,000 180,000 (30,000) - -</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-1.350648</v>
+        <v>0.15</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7681,20 +7609,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Financing costs 15,16</t>
+          <t>Share based compensation 17 - - 289,815 - -</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" s="5" t="n">
-        <v>-0.710181</v>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.955166</v>
+        <v>0.289815</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7710,12 +7640,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Share of income from investment in joint venture 12</t>
+          <t>Debt settlement 96,153 37,500 - - -</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -7725,7 +7655,7 @@
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>0.020278</v>
+        <v>0.0375</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7741,20 +7671,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Loss on recognition of sublease 15</t>
+          <t>Convertible debentures issued 15 - - - 555,537 -</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>-0.043507</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.007818</v>
+        <v>0.5555369999999999</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -7770,12 +7702,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Issued pursuant to business combination</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Changes in fair value of equity investment 8</t>
+          <t>Conversion of convertible debentures 15 12,735,246 3,454,718 - (453,946) -</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -7785,7 +7717,7 @@
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>-0.19056</v>
+        <v>3.000772</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -7801,12 +7733,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Convertible debenture deferred tax</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Convertible debenture deferred tax impact - - - (99,195) -</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -7816,7 +7748,7 @@
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.106948</v>
+        <v>-0.09919500000000001</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -7832,25 +7764,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –</t>
+          <t>Convertible debenture deferred tax</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Net loss and comprehensive loss - - - - (2,356,632)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
-        <v>108.574142</v>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>120.94241</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.265939</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.090693</v>
       </c>
     </row>
     <row r="166">
@@ -7861,25 +7793,25 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Number of      Share  Contributed  Convertible  Accumulated  Non-Controlling</t>
+          <t>Convertible debenture deferred tax</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 107,207,198 35,470,973 11,288,339 265,797 (46,308,610)</t>
+          <t>Balance at December 31,2024 129,026,039 40,468,178 11,603,526 692,495 (50,587,238)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>0.786705</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>0.070206</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.430523</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.253562</v>
       </c>
     </row>
     <row r="167">
@@ -7890,22 +7822,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Shares issued on Smile Tiger</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Share exchange – corporate acquisition 5,18 1,562,500 250,000 - - -</t>
+          <t>Shares issued on Smile Tiger business acquisition 5 104,854 125,000 - - -</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>0.125</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -7921,27 +7853,25 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Franchising Inc. business</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Share exchange – corporate acquisition 5,18 1,724,137 250,000 - - -</t>
+          <t>Franchising Inc. business acquisition 5 272,479 300,000 - - -</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>0.334382</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.034382</v>
       </c>
     </row>
     <row r="169">
@@ -7952,22 +7882,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Franchising Inc. business</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Shares held in treasury 5 - (500,000) - - -</t>
+          <t>Shares issued on Via Cibo earn-out 5 399,093 674,467 - - -</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" s="5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>0.674467</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -7983,22 +7913,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Issuance of common shares on</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Warrants exercise 18 10,000 2,000 - - -</t>
+          <t>Issuance of common shares on private placement 17 333,333 409,431 90,569 - -</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -8014,22 +7944,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Issuance of common shares on</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Share based compensation 18 - - 55,972 - -</t>
+          <t>Share based compensation 17 - - 3,692,650 - -</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>0.055972</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>3.69265</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -8045,22 +7975,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Issuance of common shares on</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Convertible debentures issued 16 - - - 424,302 -</t>
+          <t>Stock options exercise 585,000 432,837 (144,837) - -</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" s="5" t="n">
-        <v>0.424302</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.288</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -8076,12 +8006,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Issuance of common shares on</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Non-controlling interests – net loss - - - - (92,663)</t>
+          <t>Non-controlling interest buyout 5 613,468 895,663 (395,984) - -</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -8090,13 +8020,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F173" s="5" t="n">
-        <v>0.092663</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>-0.499679</v>
       </c>
     </row>
     <row r="174">
@@ -8107,17 +8037,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Issuance of common shares on</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - (1,829,333)</t>
+          <t>Treasury shares sold 5 - 222,222 (222,222) - -</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" s="5" t="n">
-        <v>-1.829333</v>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -8138,20 +8070,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Share exchange – corporate</t>
+          <t>Issuance of common shares on</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 110,503,835 35,472,973 11,344,311 690,099 (48,230,606)</t>
+          <t>Convertible debenture exercise 2,666,667 2,139,436 - (367,388) -</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" s="5" t="n">
-        <v>-0.560354</v>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F175" s="5" t="n">
-        <v>0.162869</v>
+        <v>1.772048</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -8167,22 +8101,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>combination and investment in</t>
+          <t>Convertible debenture deferred tax</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>combination and investment in joint venture 5,12 2,285,805 723,387 - - -</t>
+          <t>Convertible debenture deferred tax impact - - - 62,315 -</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" s="5" t="n">
-        <v>0.723387</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>0.062315</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -8198,27 +8132,25 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>combination and investment in</t>
+          <t>Convertible debenture deferred tax</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Warrants exercise 18 2,995,000 599,600 (600) - -</t>
+          <t>Net loss and comprehensive loss - - - - (7,691,249)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" s="5" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>-7.244958</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.446291</v>
       </c>
     </row>
     <row r="178">
@@ -8229,27 +8161,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>combination and investment in</t>
+          <t>Convertible debenture deferred tax</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Stock options exercise 18 410,000 180,000 (30,000) - -</t>
+          <t>Balance at December 31,2025 134,000,933 45,667,234 14,623,702 387,422 (58,278,487)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>2.634427</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.234556</v>
       </c>
     </row>
     <row r="179">
@@ -8260,22 +8190,20 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>combination and investment in</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Share based compensation 18 - - 289,815 - -</t>
+          <t>Product sales 3,23</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" s="5" t="n">
-        <v>0.289815</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.070922</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>7.92815</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -8291,22 +8219,20 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>combination and investment in</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Debt settlement 96,153 37,500 - - -</t>
+          <t>Franchise revenue 3,17</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" s="5" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19309</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>0.947815</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -8322,22 +8248,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>combination and investment in</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Convertible debentures issued 16 - - - 555,537 -</t>
+          <t>Consulting and services 3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="n">
-        <v>0.5555369999999999</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.147592</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0.193045</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -8353,22 +8277,24 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Conversion of convertible</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Conversion of convertible debentures 16 12,735,246 3,454,718 - (453,946) -</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
-        <v>3.000772</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.411604</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>9.06901</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -8384,22 +8310,24 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred tax impact 24 - - - (99,195) -</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>General and administrative 21</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E183" s="5" t="n">
-        <v>-0.09919500000000001</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.097402</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>3.08047</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -8415,20 +8343,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Convertible debenture deferred</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - (2,356,632)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Salaries and wages 21</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
-        <v>-2.265939</v>
+        <v>1.452481</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.090693</v>
+        <v>2.717138</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -8444,22 +8376,946 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Depreciation and Amortization 10,11</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n">
+        <v>0.440872</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>0.479568</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Expected credit loss 6,7</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" s="5" t="n">
+        <v>0.00095</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>0.239113</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Share-based compensation 18</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" s="5" t="n">
+        <v>0.055971</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>0.289815</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>6.496645</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>10.419658</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>-1.085041</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>-1.350648</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Financing costs 15,16</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>-0.710181</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>-0.955166</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Share of income from investment in joint venture 12</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>0.020278</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Loss on recognition of sublease 15</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" s="5" t="n">
+        <v>-0.043507</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>-0.007818</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Changes in fair value of equity investment 8</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>-0.19056</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>0.106948</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding –</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="5" t="n">
+        <v>108.574142</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>120.94241</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Number of      Share  Contributed  Convertible  Accumulated  Non-Controlling</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2022 107,207,198 35,470,973 11,288,339 265,797 (46,308,610)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="5" t="n">
+        <v>0.786705</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>0.070206</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate acquisition 5,18 1,562,500 250,000 - - -</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate acquisition 5,18 1,724,137 250,000 - - -</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Shares held in treasury 5 - (500,000) - - -</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Warrants exercise 18 10,000 2,000 - - -</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Share based compensation 18 - - 55,972 - -</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>0.055972</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Convertible debentures issued 16 - - - 424,302 -</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>0.424302</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Non-controlling interests – net loss - - - - (92,663)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>0.092663</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - - - (1,829,333)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="5" t="n">
+        <v>-1.829333</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Share exchange – corporate</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2023 110,503,835 35,472,973 11,344,311 690,099 (48,230,606)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>-0.560354</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>0.162869</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>combination and investment in</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>combination and investment in joint venture 5,12 2,285,805 723,387 - - -</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>0.723387</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>combination and investment in</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Warrants exercise 18 2,995,000 599,600 (600) - -</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>combination and investment in</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Stock options exercise 18 410,000 180,000 (30,000) - -</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>combination and investment in</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Share based compensation 18 - - 289,815 - -</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>0.289815</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>combination and investment in</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Debt settlement 96,153 37,500 - - -</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>combination and investment in</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Convertible debentures issued 16 - - - 555,537 -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>0.5555369999999999</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Conversion of convertible</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Conversion of convertible debentures 16 12,735,246 3,454,718 - (453,946) -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>3.000772</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
           <t>Convertible debenture deferred</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Convertible debenture deferred tax impact 24 - - - (99,195) -</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>-0.09919500000000001</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Convertible debenture deferred</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - - - (2,356,632)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>-2.265939</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.090693</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Convertible debenture deferred</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>Balance at December 31,2024 129,026,039 40,468,178 11,603,526 692,495 (50,587,238)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" s="5" t="n">
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
         <v>2.430523</v>
       </c>
-      <c r="F185" s="5" t="n">
+      <c r="F215" s="5" t="n">
         <v>0.253562</v>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
